--- a/data/trans_orig/P34B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población camina durante más de 30 minutos</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población camina (incluyendo desplazamientos al trabajo o similares) (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,9</t>
+          <t>2,47; 2,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,72</t>
+          <t>3,26; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,97</t>
+          <t>3,38; 3,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,43</t>
+          <t>2,98; 3,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,61</t>
+          <t>3,13; 3,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 3,81</t>
+          <t>3,45; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,12</t>
+          <t>2,8; 3,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 3,59</t>
+          <t>3,27; 3,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 3,81</t>
+          <t>3,51; 3,82</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 2,71</t>
+          <t>2,36; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,1</t>
+          <t>2,72; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,75</t>
+          <t>2,08; 3,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,88</t>
+          <t>2,52; 2,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 3,84</t>
+          <t>3,5; 3,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 2,67</t>
+          <t>2,4; 2,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,93</t>
+          <t>2,68; 2,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,72</t>
+          <t>2,55; 3,72</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,16</t>
+          <t>2,68; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 3,47</t>
+          <t>3,05; 3,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 4,06</t>
+          <t>3,56; 4,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,27</t>
+          <t>2,87; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,23</t>
+          <t>2,83; 3,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,33</t>
+          <t>2,69; 3,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,14</t>
+          <t>2,84; 3,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,28</t>
+          <t>3,0; 3,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,6</t>
+          <t>3,17; 3,61</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,69</t>
+          <t>2,33; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,83</t>
+          <t>3,42; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 4,23</t>
+          <t>3,83; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 2,99</t>
+          <t>2,65; 2,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 3,72</t>
+          <t>3,36; 3,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,56</t>
+          <t>3,09; 3,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 3,72</t>
+          <t>3,44; 3,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 3,82</t>
+          <t>3,49; 3,82</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 2,75</t>
+          <t>2,53; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,4</t>
+          <t>3,21; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,24</t>
+          <t>3,05; 3,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 3,54</t>
+          <t>3,3; 3,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,3</t>
+          <t>3,15; 3,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,64</t>
+          <t>3,18; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34B01-Habitat-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,93</t>
+          <t>2,47; 2,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 3,73</t>
+          <t>3,25; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 3,94</t>
+          <t>3,51; 4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,43</t>
+          <t>3,01; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 3,57</t>
+          <t>3,15; 3,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 3,8</t>
+          <t>3,42; 3,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,1</t>
+          <t>2,8; 3,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 3,59</t>
+          <t>3,27; 3,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 3,82</t>
+          <t>3,52; 3,82</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>3,79</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,76</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,74</t>
+          <t>2,34; 2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,77</t>
+          <t>3,6; 4,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 2,86</t>
+          <t>2,52; 2,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 3,84</t>
+          <t>3,58; 3,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 2,66</t>
+          <t>2,41; 2,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 2,95</t>
+          <t>2,67; 2,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,72</t>
+          <t>3,63; 3,89</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>3,63</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,12</t>
+          <t>2,7; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 3,47</t>
+          <t>3,06; 3,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,06</t>
+          <t>3,61; 4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,29</t>
+          <t>2,87; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,24</t>
+          <t>2,84; 3,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,33</t>
+          <t>3,21; 3,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,16</t>
+          <t>2,84; 3,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,3</t>
+          <t>3,0; 3,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 3,61</t>
+          <t>3,47; 3,76</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,79</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1007,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 2,69</t>
+          <t>2,32; 2,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 3,82</t>
+          <t>3,42; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 4,23</t>
+          <t>3,94; 4,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 2,99</t>
+          <t>2,63; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 3,73</t>
+          <t>3,37; 3,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,55</t>
+          <t>3,33; 3,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 3,72</t>
+          <t>3,45; 3,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 3,82</t>
+          <t>3,67; 3,91</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,72</t>
         </is>
       </c>
     </row>
@@ -1117,22 +1117,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 2,74</t>
+          <t>2,54; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 3,41</t>
+          <t>3,2; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 3,86</t>
+          <t>3,79; 4,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 2,97</t>
+          <t>2,77; 2,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 3,53</t>
+          <t>3,49; 3,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,29</t>
+          <t>3,16; 3,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 3,65</t>
+          <t>3,65; 3,79</t>
         </is>
       </c>
     </row>
